--- a/output/pdf_financials_xlsx/NOAL.xlsx
+++ b/output/pdf_financials_xlsx/NOAL.xlsx
@@ -3334,16 +3334,16 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.040592</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.040592</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.040592</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.040592</v>
       </c>
       <c r="G92" s="3" t="n">
         <v>2.702342</v>
@@ -7496,7 +7496,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -7950,7 +7954,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/NOAL.xlsx
+++ b/output/pdf_financials_xlsx/NOAL.xlsx
@@ -780,7 +780,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.083425</v>
       </c>
     </row>
     <row r="13">
@@ -1285,7 +1285,7 @@
         <v>-20.21129</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-9.753339</v>
+        <v>-9.669914</v>
       </c>
     </row>
     <row r="28">
@@ -1347,7 +1347,7 @@
         <v>-20.21129</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-9.753339</v>
+        <v>-9.669914</v>
       </c>
     </row>
     <row r="30">
@@ -1489,28 +1489,28 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.082375</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.169036</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.130389</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.051922</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>2.408418</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.357741</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>9.365665</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>5.47424</v>
       </c>
     </row>
     <row r="35">
@@ -1551,28 +1551,28 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.082375</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.169036</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.130389</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.051922</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>2.408418</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1.357741</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>9.365665</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>5.47424</v>
       </c>
     </row>
     <row r="37">
@@ -1923,10 +1923,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.082375</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.169036</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0</v>
@@ -1935,16 +1935,16 @@
         <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2.443331</v>
+        <v>0.034913</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.358865</v>
+        <v>0.001124</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>9.383305</v>
+        <v>0.01764</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>5.520072</v>
+        <v>0.045832</v>
       </c>
     </row>
     <row r="49">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -7278,7 +7278,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E42" s="5" t="n">
@@ -10116,7 +10116,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -10480,7 +10480,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">

--- a/output/pdf_financials_xlsx/NOAL.xlsx
+++ b/output/pdf_financials_xlsx/NOAL.xlsx
@@ -607,13 +607,13 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0</v>
+        <v>0.0047</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0</v>
+        <v>0.0006669999999999999</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0</v>
+        <v>0.000275</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0.183751</v>
@@ -700,13 +700,13 @@
         <v>0</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>0.0047</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
+        <v>0.0006669999999999999</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0</v>
+        <v>0.000275</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>0.183751</v>
@@ -731,13 +731,13 @@
         <v>0</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0</v>
+        <v>-0.0047</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0</v>
+        <v>-0.0006669999999999999</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0</v>
+        <v>-0.000275</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>-0.183751</v>
@@ -2644,7 +2644,7 @@
         <v>0</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0</v>
+        <v>0.004744</v>
       </c>
       <c r="H70" s="3" t="n">
         <v>0</v>
@@ -2675,7 +2675,7 @@
         <v>0</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0</v>
+        <v>0.004744</v>
       </c>
       <c r="H71" s="3" t="n">
         <v>0</v>
@@ -2799,7 +2799,7 @@
         <v>0</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.004744</v>
+        <v>0</v>
       </c>
       <c r="H75" s="3" t="n">
         <v>0.006976</v>
@@ -2965,10 +2965,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G80" s="3" t="n">
+        <v>0.0003737847661591787</v>
       </c>
       <c r="H80" s="1" t="inlineStr">
         <is>
@@ -6872,7 +6870,11 @@
           <t>Lease liabilities</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -12348,7 +12350,11 @@
           <t>Office expenses $</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
           <t>-</t>
